--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -2768,7 +2768,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -2768,7 +2768,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -2768,7 +2768,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -2768,7 +2768,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -2768,7 +2768,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -2768,7 +2768,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -4508,7 +4508,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251101_201206.xlsx
@@ -2768,7 +2768,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
